--- a/manu_sourcedata/source_data_fig4.xlsx
+++ b/manu_sourcedata/source_data_fig4.xlsx
@@ -8,14 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yyj/Doc/1_dod_dec25/manu_sourcedata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68144180-050C-D445-984B-FBEAEAB66DDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCB35C5D-7A8A-0440-BC5D-28690689B486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38980" yWindow="3780" windowWidth="27640" windowHeight="16940" activeTab="2" xr2:uid="{B6AB21C2-4AC4-4C4D-98FB-F82DCE31C267}"/>
+    <workbookView xWindow="38980" yWindow="3780" windowWidth="27640" windowHeight="16940" activeTab="5" xr2:uid="{B6AB21C2-4AC4-4C4D-98FB-F82DCE31C267}"/>
   </bookViews>
   <sheets>
     <sheet name="4a" sheetId="1" r:id="rId1"/>
     <sheet name="4b" sheetId="2" r:id="rId2"/>
-    <sheet name="4d" sheetId="3" r:id="rId3"/>
+    <sheet name="4d data" sheetId="3" r:id="rId3"/>
+    <sheet name="4d stats friedman" sheetId="4" r:id="rId4"/>
+    <sheet name="4c stats paired wilcoxon" sheetId="5" r:id="rId5"/>
+    <sheet name="4d" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="70">
   <si>
     <t>Plot_Type</t>
   </si>
@@ -116,6 +119,138 @@
   </si>
   <si>
     <t>gdT</t>
+  </si>
+  <si>
+    <t>n_complete_samples</t>
+  </si>
+  <si>
+    <t>friedman_chi2</t>
+  </si>
+  <si>
+    <t>friedman_p</t>
+  </si>
+  <si>
+    <t>mean_Immune-rich</t>
+  </si>
+  <si>
+    <t>mean_Neuroblast-rich</t>
+  </si>
+  <si>
+    <t>mean_Other</t>
+  </si>
+  <si>
+    <t>median_Immune-rich</t>
+  </si>
+  <si>
+    <t>median_Neuroblast-rich</t>
+  </si>
+  <si>
+    <t>median_Other</t>
+  </si>
+  <si>
+    <t>friedman_p_fdr_bh</t>
+  </si>
+  <si>
+    <t>Œ≥Œ¥T</t>
+  </si>
+  <si>
+    <t>domain_1</t>
+  </si>
+  <si>
+    <t>domain_2</t>
+  </si>
+  <si>
+    <t>n_pairs</t>
+  </si>
+  <si>
+    <t>wilcoxon_W</t>
+  </si>
+  <si>
+    <t>p_value</t>
+  </si>
+  <si>
+    <t>mean_1</t>
+  </si>
+  <si>
+    <t>mean_2</t>
+  </si>
+  <si>
+    <t>median_1</t>
+  </si>
+  <si>
+    <t>median_2</t>
+  </si>
+  <si>
+    <t>p_value_fdr_bh</t>
+  </si>
+  <si>
+    <t>gene</t>
+  </si>
+  <si>
+    <t>median_delta_Neuro_minus_Immune</t>
+  </si>
+  <si>
+    <t>stars</t>
+  </si>
+  <si>
+    <t>CD4</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>CD8A</t>
+  </si>
+  <si>
+    <t>TRGC2</t>
+  </si>
+  <si>
+    <t>CCR7</t>
+  </si>
+  <si>
+    <t>SELL</t>
+  </si>
+  <si>
+    <t>LEF1</t>
+  </si>
+  <si>
+    <t>TCF7</t>
+  </si>
+  <si>
+    <t>IL7R</t>
+  </si>
+  <si>
+    <t>MKI67</t>
+  </si>
+  <si>
+    <t>FOS</t>
+  </si>
+  <si>
+    <t>IFNG</t>
+  </si>
+  <si>
+    <t>GZMH</t>
+  </si>
+  <si>
+    <t>GZMB</t>
+  </si>
+  <si>
+    <t>GZMK</t>
+  </si>
+  <si>
+    <t>KLRD1</t>
+  </si>
+  <si>
+    <t>PDCD1</t>
+  </si>
+  <si>
+    <t>LAG3</t>
+  </si>
+  <si>
+    <t>TOX</t>
+  </si>
+  <si>
+    <t>TIGIT</t>
   </si>
 </sst>
 </file>
@@ -1391,4 +1526,1336 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E131BAB0-7A43-A241-B247-E07F0DD62F55}">
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2">
+        <v>10</v>
+      </c>
+      <c r="C2">
+        <v>2.5128205128205101</v>
+      </c>
+      <c r="D2">
+        <v>0.284674101531593</v>
+      </c>
+      <c r="E2">
+        <v>0.20241959187743</v>
+      </c>
+      <c r="F2">
+        <v>0.14266347582883701</v>
+      </c>
+      <c r="G2">
+        <v>0.18481443909256701</v>
+      </c>
+      <c r="H2">
+        <v>0.11015981735159799</v>
+      </c>
+      <c r="I2">
+        <v>0.107120093276331</v>
+      </c>
+      <c r="J2">
+        <v>0.117702419531687</v>
+      </c>
+      <c r="K2">
+        <v>0.284674101531593</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3">
+        <v>10</v>
+      </c>
+      <c r="C3">
+        <v>7.5384615384615401</v>
+      </c>
+      <c r="D3">
+        <v>2.30698024654864E-2</v>
+      </c>
+      <c r="E3">
+        <v>0.72075708578727804</v>
+      </c>
+      <c r="F3">
+        <v>0.64998720415621603</v>
+      </c>
+      <c r="G3">
+        <v>0.73385665045183002</v>
+      </c>
+      <c r="H3">
+        <v>0.82268668894851604</v>
+      </c>
+      <c r="I3">
+        <v>0.710403641798662</v>
+      </c>
+      <c r="J3">
+        <v>0.81771886649935399</v>
+      </c>
+      <c r="K3">
+        <v>3.8449670775810602E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4">
+        <v>10</v>
+      </c>
+      <c r="C4">
+        <v>3.55555555555555</v>
+      </c>
+      <c r="D4">
+        <v>0.16901331540606501</v>
+      </c>
+      <c r="E4">
+        <v>1.25548883729081E-2</v>
+      </c>
+      <c r="F4">
+        <v>1.6213275541720799E-2</v>
+      </c>
+      <c r="G4">
+        <v>1.0663539449034899E-2</v>
+      </c>
+      <c r="H4">
+        <v>3.4176613729280801E-3</v>
+      </c>
+      <c r="I4">
+        <v>9.2416833761330194E-3</v>
+      </c>
+      <c r="J4">
+        <v>5.3313441405969603E-3</v>
+      </c>
+      <c r="K4">
+        <v>0.21126664425758199</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>12.967741935483801</v>
+      </c>
+      <c r="D5">
+        <v>1.5278848244586699E-3</v>
+      </c>
+      <c r="E5">
+        <v>3.8639691916095599E-3</v>
+      </c>
+      <c r="F5">
+        <v>1.7128348769313701E-2</v>
+      </c>
+      <c r="G5">
+        <v>6.9652204772857598E-3</v>
+      </c>
+      <c r="H5">
+        <v>4.5430101111095498E-4</v>
+      </c>
+      <c r="I5">
+        <v>6.9635694878287697E-3</v>
+      </c>
+      <c r="J5">
+        <v>1.3866257558170099E-3</v>
+      </c>
+      <c r="K5">
+        <v>3.81971206114668E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6">
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>14.307692307692299</v>
+      </c>
+      <c r="D6">
+        <v>7.8185117107816104E-4</v>
+      </c>
+      <c r="E6">
+        <v>6.04044647707732E-2</v>
+      </c>
+      <c r="F6">
+        <v>0.17400769570391</v>
+      </c>
+      <c r="G6">
+        <v>6.3700150529281699E-2</v>
+      </c>
+      <c r="H6">
+        <v>8.3778986855825403E-3</v>
+      </c>
+      <c r="I6">
+        <v>0.14522613412805399</v>
+      </c>
+      <c r="J6">
+        <v>3.7182553894783102E-2</v>
+      </c>
+      <c r="K6">
+        <v>3.81971206114668E-3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11593CD8-EDF9-E441-B915-88CC36066F61}">
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2">
+        <v>10</v>
+      </c>
+      <c r="E2">
+        <v>16</v>
+      </c>
+      <c r="F2">
+        <v>0.275390625</v>
+      </c>
+      <c r="G2">
+        <v>0.20241959187743</v>
+      </c>
+      <c r="H2">
+        <v>0.14266347582883701</v>
+      </c>
+      <c r="I2">
+        <v>0.11015981735159799</v>
+      </c>
+      <c r="J2">
+        <v>0.107120093276331</v>
+      </c>
+      <c r="K2">
+        <v>0.37109375</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3">
+        <v>10</v>
+      </c>
+      <c r="E3">
+        <v>18</v>
+      </c>
+      <c r="F3">
+        <v>0.65234375</v>
+      </c>
+      <c r="G3">
+        <v>0.20241959187743</v>
+      </c>
+      <c r="H3">
+        <v>0.18481443909256701</v>
+      </c>
+      <c r="I3">
+        <v>0.11015981735159799</v>
+      </c>
+      <c r="J3">
+        <v>0.117702419531687</v>
+      </c>
+      <c r="K3">
+        <v>0.69893973214285698</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4">
+        <v>10</v>
+      </c>
+      <c r="E4">
+        <v>8</v>
+      </c>
+      <c r="F4">
+        <v>4.8828125E-2</v>
+      </c>
+      <c r="G4">
+        <v>0.14266347582883701</v>
+      </c>
+      <c r="H4">
+        <v>0.18481443909256701</v>
+      </c>
+      <c r="I4">
+        <v>0.107120093276331</v>
+      </c>
+      <c r="J4">
+        <v>0.117702419531687</v>
+      </c>
+      <c r="K4">
+        <v>0.1025390625</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5">
+        <v>10</v>
+      </c>
+      <c r="E5">
+        <v>8</v>
+      </c>
+      <c r="F5">
+        <v>4.8828125E-2</v>
+      </c>
+      <c r="G5">
+        <v>0.72075708578727804</v>
+      </c>
+      <c r="H5">
+        <v>0.64998720415621603</v>
+      </c>
+      <c r="I5">
+        <v>0.82268668894851604</v>
+      </c>
+      <c r="J5">
+        <v>0.710403641798662</v>
+      </c>
+      <c r="K5">
+        <v>0.1025390625</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>20</v>
+      </c>
+      <c r="F6">
+        <v>0.8203125</v>
+      </c>
+      <c r="G6">
+        <v>0.72075708578727804</v>
+      </c>
+      <c r="H6">
+        <v>0.73385665045183002</v>
+      </c>
+      <c r="I6">
+        <v>0.82268668894851604</v>
+      </c>
+      <c r="J6">
+        <v>0.81771886649935399</v>
+      </c>
+      <c r="K6">
+        <v>0.8203125</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7">
+        <v>10</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>5.859375E-3</v>
+      </c>
+      <c r="G7">
+        <v>0.64998720415621603</v>
+      </c>
+      <c r="H7">
+        <v>0.73385665045183002</v>
+      </c>
+      <c r="I7">
+        <v>0.710403641798662</v>
+      </c>
+      <c r="J7">
+        <v>0.81771886649935399</v>
+      </c>
+      <c r="K7">
+        <v>2.9296875E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8">
+        <v>10</v>
+      </c>
+      <c r="E8">
+        <v>10</v>
+      </c>
+      <c r="F8">
+        <v>0.1640625</v>
+      </c>
+      <c r="G8">
+        <v>1.25548883729081E-2</v>
+      </c>
+      <c r="H8">
+        <v>1.6213275541720799E-2</v>
+      </c>
+      <c r="I8">
+        <v>3.4176613729280801E-3</v>
+      </c>
+      <c r="J8">
+        <v>9.2416833761330194E-3</v>
+      </c>
+      <c r="K8">
+        <v>0.24609375</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9">
+        <v>10</v>
+      </c>
+      <c r="E9">
+        <v>16</v>
+      </c>
+      <c r="F9">
+        <v>0.49609375</v>
+      </c>
+      <c r="G9">
+        <v>1.25548883729081E-2</v>
+      </c>
+      <c r="H9">
+        <v>1.0663539449034899E-2</v>
+      </c>
+      <c r="I9">
+        <v>3.4176613729280801E-3</v>
+      </c>
+      <c r="J9">
+        <v>5.3313441405969603E-3</v>
+      </c>
+      <c r="K9">
+        <v>0.57241586538461497</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10">
+        <v>10</v>
+      </c>
+      <c r="E10">
+        <v>6</v>
+      </c>
+      <c r="F10">
+        <v>5.46875E-2</v>
+      </c>
+      <c r="G10">
+        <v>1.6213275541720799E-2</v>
+      </c>
+      <c r="H10">
+        <v>1.0663539449034899E-2</v>
+      </c>
+      <c r="I10">
+        <v>9.2416833761330194E-3</v>
+      </c>
+      <c r="J10">
+        <v>5.3313441405969603E-3</v>
+      </c>
+      <c r="K10">
+        <v>0.1025390625</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11">
+        <v>10</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>7.8125E-3</v>
+      </c>
+      <c r="G11">
+        <v>3.8639691916095599E-3</v>
+      </c>
+      <c r="H11">
+        <v>1.7128348769313701E-2</v>
+      </c>
+      <c r="I11">
+        <v>4.5430101111095498E-4</v>
+      </c>
+      <c r="J11">
+        <v>6.9635694878287697E-3</v>
+      </c>
+      <c r="K11">
+        <v>2.9296875E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12">
+        <v>10</v>
+      </c>
+      <c r="E12">
+        <v>7</v>
+      </c>
+      <c r="F12">
+        <v>0.296875</v>
+      </c>
+      <c r="G12">
+        <v>3.8639691916095599E-3</v>
+      </c>
+      <c r="H12">
+        <v>6.9652204772857598E-3</v>
+      </c>
+      <c r="I12">
+        <v>4.5430101111095498E-4</v>
+      </c>
+      <c r="J12">
+        <v>1.3866257558170099E-3</v>
+      </c>
+      <c r="K12">
+        <v>0.37109375</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13">
+        <v>10</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>7.8125E-3</v>
+      </c>
+      <c r="G13">
+        <v>1.7128348769313701E-2</v>
+      </c>
+      <c r="H13">
+        <v>6.9652204772857598E-3</v>
+      </c>
+      <c r="I13">
+        <v>6.9635694878287697E-3</v>
+      </c>
+      <c r="J13">
+        <v>1.3866257558170099E-3</v>
+      </c>
+      <c r="K13">
+        <v>2.9296875E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14">
+        <v>10</v>
+      </c>
+      <c r="E14">
+        <v>5</v>
+      </c>
+      <c r="F14">
+        <v>1.953125E-2</v>
+      </c>
+      <c r="G14">
+        <v>6.04044647707732E-2</v>
+      </c>
+      <c r="H14">
+        <v>0.17400769570391</v>
+      </c>
+      <c r="I14">
+        <v>8.3778986855825403E-3</v>
+      </c>
+      <c r="J14">
+        <v>0.14522613412805399</v>
+      </c>
+      <c r="K14">
+        <v>5.859375E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15">
+        <v>10</v>
+      </c>
+      <c r="E15">
+        <v>9</v>
+      </c>
+      <c r="F15">
+        <v>0.12890625</v>
+      </c>
+      <c r="G15">
+        <v>6.04044647707732E-2</v>
+      </c>
+      <c r="H15">
+        <v>6.3700150529281699E-2</v>
+      </c>
+      <c r="I15">
+        <v>8.3778986855825403E-3</v>
+      </c>
+      <c r="J15">
+        <v>3.7182553894783102E-2</v>
+      </c>
+      <c r="K15">
+        <v>0.21484375</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16">
+        <v>10</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>1.953125E-3</v>
+      </c>
+      <c r="G16">
+        <v>0.17400769570391</v>
+      </c>
+      <c r="H16">
+        <v>6.3700150529281699E-2</v>
+      </c>
+      <c r="I16">
+        <v>0.14522613412805399</v>
+      </c>
+      <c r="J16">
+        <v>3.7182553894783102E-2</v>
+      </c>
+      <c r="K16">
+        <v>2.9296875E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDAE2F8F-E091-4D4D-89EE-A93590B014AD}">
+  <dimension ref="A1:I20"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2">
+        <v>10</v>
+      </c>
+      <c r="C2">
+        <v>2.46260285377502</v>
+      </c>
+      <c r="D2">
+        <v>1.8623615503311099</v>
+      </c>
+      <c r="E2">
+        <v>-0.54142165184020996</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>1.953125E-3</v>
+      </c>
+      <c r="H2">
+        <v>2.4739583333333301E-2</v>
+      </c>
+      <c r="I2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3">
+        <v>10</v>
+      </c>
+      <c r="C3">
+        <v>2.37063312530517</v>
+      </c>
+      <c r="D3">
+        <v>2.69232130050659</v>
+      </c>
+      <c r="E3">
+        <v>-4.7664642333984299E-2</v>
+      </c>
+      <c r="F3">
+        <v>24</v>
+      </c>
+      <c r="G3">
+        <v>0.76953125</v>
+      </c>
+      <c r="H3">
+        <v>0.86006433823529405</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4">
+        <v>10</v>
+      </c>
+      <c r="C4">
+        <v>2.5768327713012602</v>
+      </c>
+      <c r="D4">
+        <v>2.4906578063964799</v>
+      </c>
+      <c r="E4">
+        <v>7.9481363296508706E-2</v>
+      </c>
+      <c r="F4">
+        <v>25</v>
+      </c>
+      <c r="G4">
+        <v>0.845703125</v>
+      </c>
+      <c r="H4">
+        <v>0.89268663194444398</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>1.7404419183730999</v>
+      </c>
+      <c r="D5">
+        <v>1.5143289566039999</v>
+      </c>
+      <c r="E5">
+        <v>-0.330892324447631</v>
+      </c>
+      <c r="F5">
+        <v>21</v>
+      </c>
+      <c r="G5">
+        <v>0.556640625</v>
+      </c>
+      <c r="H5">
+        <v>0.7421875</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6">
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>2.52273249626159</v>
+      </c>
+      <c r="D6">
+        <v>2.2136936187744101</v>
+      </c>
+      <c r="E6">
+        <v>-0.25080913305282498</v>
+      </c>
+      <c r="F6">
+        <v>13</v>
+      </c>
+      <c r="G6">
+        <v>0.16015625</v>
+      </c>
+      <c r="H6">
+        <v>0.30429687500000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7">
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <v>2.5341942310333199</v>
+      </c>
+      <c r="D7">
+        <v>2.3353459835052401</v>
+      </c>
+      <c r="E7">
+        <v>-0.27436995506286599</v>
+      </c>
+      <c r="F7">
+        <v>15</v>
+      </c>
+      <c r="G7">
+        <v>0.232421875</v>
+      </c>
+      <c r="H7">
+        <v>0.40145596590909</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8">
+        <v>10</v>
+      </c>
+      <c r="C8">
+        <v>2.6894602775573699</v>
+      </c>
+      <c r="D8">
+        <v>2.3924431800842201</v>
+      </c>
+      <c r="E8">
+        <v>-0.544000923633575</v>
+      </c>
+      <c r="F8">
+        <v>11</v>
+      </c>
+      <c r="G8">
+        <v>0.10546875</v>
+      </c>
+      <c r="H8">
+        <v>0.22265625</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9">
+        <v>10</v>
+      </c>
+      <c r="C9">
+        <v>3.2356688976287802</v>
+      </c>
+      <c r="D9">
+        <v>2.9809296131134002</v>
+      </c>
+      <c r="E9">
+        <v>-9.8764538764953599E-2</v>
+      </c>
+      <c r="F9">
+        <v>16</v>
+      </c>
+      <c r="G9">
+        <v>0.275390625</v>
+      </c>
+      <c r="H9">
+        <v>0.43603515625</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10">
+        <v>10</v>
+      </c>
+      <c r="C10">
+        <v>0.62796431779861395</v>
+      </c>
+      <c r="D10">
+        <v>0.89421451091766302</v>
+      </c>
+      <c r="E10">
+        <v>0.39729547500610302</v>
+      </c>
+      <c r="F10">
+        <v>10</v>
+      </c>
+      <c r="G10">
+        <v>8.3984375E-2</v>
+      </c>
+      <c r="H10">
+        <v>0.22265625</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11">
+        <v>2.0139503479003902</v>
+      </c>
+      <c r="D11">
+        <v>1.2366625070571899</v>
+      </c>
+      <c r="E11">
+        <v>-0.65410113334655695</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>3.90625E-3</v>
+      </c>
+      <c r="H11">
+        <v>2.4739583333333301E-2</v>
+      </c>
+      <c r="I11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12">
+        <v>10</v>
+      </c>
+      <c r="C12">
+        <v>0.285680592060089</v>
+      </c>
+      <c r="D12">
+        <v>0.35772219300269997</v>
+      </c>
+      <c r="E12">
+        <v>6.6190157085657102E-3</v>
+      </c>
+      <c r="F12">
+        <v>15</v>
+      </c>
+      <c r="G12">
+        <v>0.42578125</v>
+      </c>
+      <c r="H12">
+        <v>0.62229567307692302</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13">
+        <v>10</v>
+      </c>
+      <c r="C13">
+        <v>1.03546738624572</v>
+      </c>
+      <c r="D13">
+        <v>1.3062003850936801</v>
+      </c>
+      <c r="E13">
+        <v>0.14636893570423101</v>
+      </c>
+      <c r="F13">
+        <v>11</v>
+      </c>
+      <c r="G13">
+        <v>0.10546875</v>
+      </c>
+      <c r="H13">
+        <v>0.22265625</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14">
+        <v>10</v>
+      </c>
+      <c r="C14">
+        <v>0.57797950506210305</v>
+      </c>
+      <c r="D14">
+        <v>0.80016165971755904</v>
+      </c>
+      <c r="E14">
+        <v>8.2571320235729204E-2</v>
+      </c>
+      <c r="F14">
+        <v>6</v>
+      </c>
+      <c r="G14">
+        <v>2.734375E-2</v>
+      </c>
+      <c r="H14">
+        <v>0.1298828125</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>64</v>
+      </c>
+      <c r="B15">
+        <v>10</v>
+      </c>
+      <c r="C15">
+        <v>1.88420009613037</v>
+      </c>
+      <c r="D15">
+        <v>1.93773877620697</v>
+      </c>
+      <c r="E15">
+        <v>-0.31544423103332497</v>
+      </c>
+      <c r="F15">
+        <v>22</v>
+      </c>
+      <c r="G15">
+        <v>0.625</v>
+      </c>
+      <c r="H15">
+        <v>0.7421875</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16">
+        <v>10</v>
+      </c>
+      <c r="C16">
+        <v>1.6306470632553101</v>
+      </c>
+      <c r="D16">
+        <v>1.7904590368270801</v>
+      </c>
+      <c r="E16">
+        <v>0.25005236268043501</v>
+      </c>
+      <c r="F16">
+        <v>10</v>
+      </c>
+      <c r="G16">
+        <v>8.3984375E-2</v>
+      </c>
+      <c r="H16">
+        <v>0.22265625</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>66</v>
+      </c>
+      <c r="B17">
+        <v>10</v>
+      </c>
+      <c r="C17">
+        <v>0.54469358921051003</v>
+      </c>
+      <c r="D17">
+        <v>0.53849822282791104</v>
+      </c>
+      <c r="E17">
+        <v>2.66434252262115E-3</v>
+      </c>
+      <c r="F17">
+        <v>26</v>
+      </c>
+      <c r="G17">
+        <v>0.921875</v>
+      </c>
+      <c r="H17">
+        <v>0.921875</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>67</v>
+      </c>
+      <c r="B18">
+        <v>10</v>
+      </c>
+      <c r="C18">
+        <v>1.00748610496521</v>
+      </c>
+      <c r="D18">
+        <v>1.43984222412109</v>
+      </c>
+      <c r="E18">
+        <v>0.231475800275802</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>3.90625E-3</v>
+      </c>
+      <c r="H18">
+        <v>2.4739583333333301E-2</v>
+      </c>
+      <c r="I18" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>68</v>
+      </c>
+      <c r="B19">
+        <v>10</v>
+      </c>
+      <c r="C19">
+        <v>1.3361523151397701</v>
+      </c>
+      <c r="D19">
+        <v>1.5046077966689999</v>
+      </c>
+      <c r="E19">
+        <v>0.149342715740203</v>
+      </c>
+      <c r="F19">
+        <v>10</v>
+      </c>
+      <c r="G19">
+        <v>8.3984375E-2</v>
+      </c>
+      <c r="H19">
+        <v>0.22265625</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20">
+        <v>10</v>
+      </c>
+      <c r="C20">
+        <v>1.56668889522552</v>
+      </c>
+      <c r="D20">
+        <v>1.5258419513702299</v>
+      </c>
+      <c r="E20">
+        <v>-0.17297682166099501</v>
+      </c>
+      <c r="F20">
+        <v>22</v>
+      </c>
+      <c r="G20">
+        <v>0.625</v>
+      </c>
+      <c r="H20">
+        <v>0.7421875</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/manu_sourcedata/source_data_fig4.xlsx
+++ b/manu_sourcedata/source_data_fig4.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yyj/Doc/1_dod_dec25/manu_sourcedata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCB35C5D-7A8A-0440-BC5D-28690689B486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A9E7667-7051-C14D-AD2D-14FCD9C3B601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38980" yWindow="3780" windowWidth="27640" windowHeight="16940" activeTab="5" xr2:uid="{B6AB21C2-4AC4-4C4D-98FB-F82DCE31C267}"/>
+    <workbookView xWindow="38980" yWindow="3780" windowWidth="27640" windowHeight="16940" activeTab="2" xr2:uid="{B6AB21C2-4AC4-4C4D-98FB-F82DCE31C267}"/>
   </bookViews>
   <sheets>
     <sheet name="4a" sheetId="1" r:id="rId1"/>
     <sheet name="4b" sheetId="2" r:id="rId2"/>
-    <sheet name="4d data" sheetId="3" r:id="rId3"/>
-    <sheet name="4d stats friedman" sheetId="4" r:id="rId4"/>
-    <sheet name="4c stats paired wilcoxon" sheetId="5" r:id="rId5"/>
-    <sheet name="4d" sheetId="6" r:id="rId6"/>
+    <sheet name="4c stats paired wilcoxon" sheetId="5" r:id="rId3"/>
+    <sheet name="4d data" sheetId="3" r:id="rId4"/>
+    <sheet name="4d stats friedman" sheetId="4" r:id="rId5"/>
+    <sheet name="4d stats paired wilcoxon" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="69">
   <si>
     <t>Plot_Type</t>
   </si>
@@ -149,9 +149,6 @@
   </si>
   <si>
     <t>friedman_p_fdr_bh</t>
-  </si>
-  <si>
-    <t>Œ≥Œ¥T</t>
   </si>
   <si>
     <t>domain_1</t>
@@ -286,8 +283,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1415,6 +1413,576 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11593CD8-EDF9-E441-B915-88CC36066F61}">
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" t="s">
+        <v>44</v>
+      </c>
+      <c r="K1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2">
+        <v>10</v>
+      </c>
+      <c r="E2">
+        <v>16</v>
+      </c>
+      <c r="F2">
+        <v>0.275390625</v>
+      </c>
+      <c r="G2">
+        <v>0.20241959187743</v>
+      </c>
+      <c r="H2">
+        <v>0.14266347582883701</v>
+      </c>
+      <c r="I2">
+        <v>0.11015981735159799</v>
+      </c>
+      <c r="J2">
+        <v>0.107120093276331</v>
+      </c>
+      <c r="K2">
+        <v>0.37109375</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3">
+        <v>10</v>
+      </c>
+      <c r="E3">
+        <v>18</v>
+      </c>
+      <c r="F3">
+        <v>0.65234375</v>
+      </c>
+      <c r="G3">
+        <v>0.20241959187743</v>
+      </c>
+      <c r="H3">
+        <v>0.18481443909256701</v>
+      </c>
+      <c r="I3">
+        <v>0.11015981735159799</v>
+      </c>
+      <c r="J3">
+        <v>0.117702419531687</v>
+      </c>
+      <c r="K3">
+        <v>0.69893973214285698</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4">
+        <v>10</v>
+      </c>
+      <c r="E4">
+        <v>8</v>
+      </c>
+      <c r="F4">
+        <v>4.8828125E-2</v>
+      </c>
+      <c r="G4">
+        <v>0.14266347582883701</v>
+      </c>
+      <c r="H4">
+        <v>0.18481443909256701</v>
+      </c>
+      <c r="I4">
+        <v>0.107120093276331</v>
+      </c>
+      <c r="J4">
+        <v>0.117702419531687</v>
+      </c>
+      <c r="K4">
+        <v>0.1025390625</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5">
+        <v>10</v>
+      </c>
+      <c r="E5">
+        <v>8</v>
+      </c>
+      <c r="F5">
+        <v>4.8828125E-2</v>
+      </c>
+      <c r="G5">
+        <v>0.72075708578727804</v>
+      </c>
+      <c r="H5">
+        <v>0.64998720415621603</v>
+      </c>
+      <c r="I5">
+        <v>0.82268668894851604</v>
+      </c>
+      <c r="J5">
+        <v>0.710403641798662</v>
+      </c>
+      <c r="K5">
+        <v>0.1025390625</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>20</v>
+      </c>
+      <c r="F6">
+        <v>0.8203125</v>
+      </c>
+      <c r="G6">
+        <v>0.72075708578727804</v>
+      </c>
+      <c r="H6">
+        <v>0.73385665045183002</v>
+      </c>
+      <c r="I6">
+        <v>0.82268668894851604</v>
+      </c>
+      <c r="J6">
+        <v>0.81771886649935399</v>
+      </c>
+      <c r="K6">
+        <v>0.8203125</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7">
+        <v>10</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>5.859375E-3</v>
+      </c>
+      <c r="G7">
+        <v>0.64998720415621603</v>
+      </c>
+      <c r="H7">
+        <v>0.73385665045183002</v>
+      </c>
+      <c r="I7">
+        <v>0.710403641798662</v>
+      </c>
+      <c r="J7">
+        <v>0.81771886649935399</v>
+      </c>
+      <c r="K7" s="1">
+        <v>2.9296875E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8">
+        <v>10</v>
+      </c>
+      <c r="E8">
+        <v>10</v>
+      </c>
+      <c r="F8">
+        <v>0.1640625</v>
+      </c>
+      <c r="G8">
+        <v>1.25548883729081E-2</v>
+      </c>
+      <c r="H8">
+        <v>1.6213275541720799E-2</v>
+      </c>
+      <c r="I8">
+        <v>3.4176613729280801E-3</v>
+      </c>
+      <c r="J8">
+        <v>9.2416833761330194E-3</v>
+      </c>
+      <c r="K8" s="1">
+        <v>0.24609375</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9">
+        <v>10</v>
+      </c>
+      <c r="E9">
+        <v>16</v>
+      </c>
+      <c r="F9">
+        <v>0.49609375</v>
+      </c>
+      <c r="G9">
+        <v>1.25548883729081E-2</v>
+      </c>
+      <c r="H9">
+        <v>1.0663539449034899E-2</v>
+      </c>
+      <c r="I9">
+        <v>3.4176613729280801E-3</v>
+      </c>
+      <c r="J9">
+        <v>5.3313441405969603E-3</v>
+      </c>
+      <c r="K9" s="1">
+        <v>0.57241586538461497</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10">
+        <v>10</v>
+      </c>
+      <c r="E10">
+        <v>6</v>
+      </c>
+      <c r="F10">
+        <v>5.46875E-2</v>
+      </c>
+      <c r="G10">
+        <v>1.6213275541720799E-2</v>
+      </c>
+      <c r="H10">
+        <v>1.0663539449034899E-2</v>
+      </c>
+      <c r="I10">
+        <v>9.2416833761330194E-3</v>
+      </c>
+      <c r="J10">
+        <v>5.3313441405969603E-3</v>
+      </c>
+      <c r="K10" s="1">
+        <v>0.1025390625</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11">
+        <v>10</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>7.8125E-3</v>
+      </c>
+      <c r="G11">
+        <v>3.8639691916095599E-3</v>
+      </c>
+      <c r="H11">
+        <v>1.7128348769313701E-2</v>
+      </c>
+      <c r="I11">
+        <v>4.5430101111095498E-4</v>
+      </c>
+      <c r="J11">
+        <v>6.9635694878287697E-3</v>
+      </c>
+      <c r="K11" s="1">
+        <v>2.9296875E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12">
+        <v>10</v>
+      </c>
+      <c r="E12">
+        <v>7</v>
+      </c>
+      <c r="F12">
+        <v>0.296875</v>
+      </c>
+      <c r="G12">
+        <v>3.8639691916095599E-3</v>
+      </c>
+      <c r="H12">
+        <v>6.9652204772857598E-3</v>
+      </c>
+      <c r="I12">
+        <v>4.5430101111095498E-4</v>
+      </c>
+      <c r="J12">
+        <v>1.3866257558170099E-3</v>
+      </c>
+      <c r="K12" s="1">
+        <v>0.37109375</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13">
+        <v>10</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>7.8125E-3</v>
+      </c>
+      <c r="G13">
+        <v>1.7128348769313701E-2</v>
+      </c>
+      <c r="H13">
+        <v>6.9652204772857598E-3</v>
+      </c>
+      <c r="I13">
+        <v>6.9635694878287697E-3</v>
+      </c>
+      <c r="J13">
+        <v>1.3866257558170099E-3</v>
+      </c>
+      <c r="K13" s="1">
+        <v>2.9296875E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14">
+        <v>10</v>
+      </c>
+      <c r="E14">
+        <v>5</v>
+      </c>
+      <c r="F14">
+        <v>1.953125E-2</v>
+      </c>
+      <c r="G14">
+        <v>6.04044647707732E-2</v>
+      </c>
+      <c r="H14">
+        <v>0.17400769570391</v>
+      </c>
+      <c r="I14">
+        <v>8.3778986855825403E-3</v>
+      </c>
+      <c r="J14">
+        <v>0.14522613412805399</v>
+      </c>
+      <c r="K14" s="1">
+        <v>5.859375E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15">
+        <v>10</v>
+      </c>
+      <c r="E15">
+        <v>9</v>
+      </c>
+      <c r="F15">
+        <v>0.12890625</v>
+      </c>
+      <c r="G15">
+        <v>6.04044647707732E-2</v>
+      </c>
+      <c r="H15">
+        <v>6.3700150529281699E-2</v>
+      </c>
+      <c r="I15">
+        <v>8.3778986855825403E-3</v>
+      </c>
+      <c r="J15">
+        <v>3.7182553894783102E-2</v>
+      </c>
+      <c r="K15" s="1">
+        <v>0.21484375</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16">
+        <v>10</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>1.953125E-3</v>
+      </c>
+      <c r="G16">
+        <v>0.17400769570391</v>
+      </c>
+      <c r="H16">
+        <v>6.3700150529281699E-2</v>
+      </c>
+      <c r="I16">
+        <v>0.14522613412805399</v>
+      </c>
+      <c r="J16">
+        <v>3.7182553894783102E-2</v>
+      </c>
+      <c r="K16" s="1">
+        <v>2.9296875E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7690145-C032-194A-B5D2-8A84EB49D220}">
   <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -1528,7 +2096,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E131BAB0-7A43-A241-B247-E07F0DD62F55}">
   <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -1710,7 +2278,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B6">
         <v>10</v>
@@ -1741,576 +2309,6 @@
       </c>
       <c r="K6">
         <v>3.81971206114668E-3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11593CD8-EDF9-E441-B915-88CC36066F61}">
-  <dimension ref="A1:K16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H1" t="s">
-        <v>43</v>
-      </c>
-      <c r="I1" t="s">
-        <v>44</v>
-      </c>
-      <c r="J1" t="s">
-        <v>45</v>
-      </c>
-      <c r="K1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2">
-        <v>10</v>
-      </c>
-      <c r="E2">
-        <v>16</v>
-      </c>
-      <c r="F2">
-        <v>0.275390625</v>
-      </c>
-      <c r="G2">
-        <v>0.20241959187743</v>
-      </c>
-      <c r="H2">
-        <v>0.14266347582883701</v>
-      </c>
-      <c r="I2">
-        <v>0.11015981735159799</v>
-      </c>
-      <c r="J2">
-        <v>0.107120093276331</v>
-      </c>
-      <c r="K2">
-        <v>0.37109375</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3">
-        <v>10</v>
-      </c>
-      <c r="E3">
-        <v>18</v>
-      </c>
-      <c r="F3">
-        <v>0.65234375</v>
-      </c>
-      <c r="G3">
-        <v>0.20241959187743</v>
-      </c>
-      <c r="H3">
-        <v>0.18481443909256701</v>
-      </c>
-      <c r="I3">
-        <v>0.11015981735159799</v>
-      </c>
-      <c r="J3">
-        <v>0.117702419531687</v>
-      </c>
-      <c r="K3">
-        <v>0.69893973214285698</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4">
-        <v>10</v>
-      </c>
-      <c r="E4">
-        <v>8</v>
-      </c>
-      <c r="F4">
-        <v>4.8828125E-2</v>
-      </c>
-      <c r="G4">
-        <v>0.14266347582883701</v>
-      </c>
-      <c r="H4">
-        <v>0.18481443909256701</v>
-      </c>
-      <c r="I4">
-        <v>0.107120093276331</v>
-      </c>
-      <c r="J4">
-        <v>0.117702419531687</v>
-      </c>
-      <c r="K4">
-        <v>0.1025390625</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5">
-        <v>10</v>
-      </c>
-      <c r="E5">
-        <v>8</v>
-      </c>
-      <c r="F5">
-        <v>4.8828125E-2</v>
-      </c>
-      <c r="G5">
-        <v>0.72075708578727804</v>
-      </c>
-      <c r="H5">
-        <v>0.64998720415621603</v>
-      </c>
-      <c r="I5">
-        <v>0.82268668894851604</v>
-      </c>
-      <c r="J5">
-        <v>0.710403641798662</v>
-      </c>
-      <c r="K5">
-        <v>0.1025390625</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6">
-        <v>10</v>
-      </c>
-      <c r="E6">
-        <v>20</v>
-      </c>
-      <c r="F6">
-        <v>0.8203125</v>
-      </c>
-      <c r="G6">
-        <v>0.72075708578727804</v>
-      </c>
-      <c r="H6">
-        <v>0.73385665045183002</v>
-      </c>
-      <c r="I6">
-        <v>0.82268668894851604</v>
-      </c>
-      <c r="J6">
-        <v>0.81771886649935399</v>
-      </c>
-      <c r="K6">
-        <v>0.8203125</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7">
-        <v>10</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7">
-        <v>5.859375E-3</v>
-      </c>
-      <c r="G7">
-        <v>0.64998720415621603</v>
-      </c>
-      <c r="H7">
-        <v>0.73385665045183002</v>
-      </c>
-      <c r="I7">
-        <v>0.710403641798662</v>
-      </c>
-      <c r="J7">
-        <v>0.81771886649935399</v>
-      </c>
-      <c r="K7">
-        <v>2.9296875E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8">
-        <v>10</v>
-      </c>
-      <c r="E8">
-        <v>10</v>
-      </c>
-      <c r="F8">
-        <v>0.1640625</v>
-      </c>
-      <c r="G8">
-        <v>1.25548883729081E-2</v>
-      </c>
-      <c r="H8">
-        <v>1.6213275541720799E-2</v>
-      </c>
-      <c r="I8">
-        <v>3.4176613729280801E-3</v>
-      </c>
-      <c r="J8">
-        <v>9.2416833761330194E-3</v>
-      </c>
-      <c r="K8">
-        <v>0.24609375</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9">
-        <v>10</v>
-      </c>
-      <c r="E9">
-        <v>16</v>
-      </c>
-      <c r="F9">
-        <v>0.49609375</v>
-      </c>
-      <c r="G9">
-        <v>1.25548883729081E-2</v>
-      </c>
-      <c r="H9">
-        <v>1.0663539449034899E-2</v>
-      </c>
-      <c r="I9">
-        <v>3.4176613729280801E-3</v>
-      </c>
-      <c r="J9">
-        <v>5.3313441405969603E-3</v>
-      </c>
-      <c r="K9">
-        <v>0.57241586538461497</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10">
-        <v>10</v>
-      </c>
-      <c r="E10">
-        <v>6</v>
-      </c>
-      <c r="F10">
-        <v>5.46875E-2</v>
-      </c>
-      <c r="G10">
-        <v>1.6213275541720799E-2</v>
-      </c>
-      <c r="H10">
-        <v>1.0663539449034899E-2</v>
-      </c>
-      <c r="I10">
-        <v>9.2416833761330194E-3</v>
-      </c>
-      <c r="J10">
-        <v>5.3313441405969603E-3</v>
-      </c>
-      <c r="K10">
-        <v>0.1025390625</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11">
-        <v>10</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>7.8125E-3</v>
-      </c>
-      <c r="G11">
-        <v>3.8639691916095599E-3</v>
-      </c>
-      <c r="H11">
-        <v>1.7128348769313701E-2</v>
-      </c>
-      <c r="I11">
-        <v>4.5430101111095498E-4</v>
-      </c>
-      <c r="J11">
-        <v>6.9635694878287697E-3</v>
-      </c>
-      <c r="K11">
-        <v>2.9296875E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12">
-        <v>10</v>
-      </c>
-      <c r="E12">
-        <v>7</v>
-      </c>
-      <c r="F12">
-        <v>0.296875</v>
-      </c>
-      <c r="G12">
-        <v>3.8639691916095599E-3</v>
-      </c>
-      <c r="H12">
-        <v>6.9652204772857598E-3</v>
-      </c>
-      <c r="I12">
-        <v>4.5430101111095498E-4</v>
-      </c>
-      <c r="J12">
-        <v>1.3866257558170099E-3</v>
-      </c>
-      <c r="K12">
-        <v>0.37109375</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13">
-        <v>10</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>7.8125E-3</v>
-      </c>
-      <c r="G13">
-        <v>1.7128348769313701E-2</v>
-      </c>
-      <c r="H13">
-        <v>6.9652204772857598E-3</v>
-      </c>
-      <c r="I13">
-        <v>6.9635694878287697E-3</v>
-      </c>
-      <c r="J13">
-        <v>1.3866257558170099E-3</v>
-      </c>
-      <c r="K13">
-        <v>2.9296875E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>36</v>
-      </c>
-      <c r="B14" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14">
-        <v>10</v>
-      </c>
-      <c r="E14">
-        <v>5</v>
-      </c>
-      <c r="F14">
-        <v>1.953125E-2</v>
-      </c>
-      <c r="G14">
-        <v>6.04044647707732E-2</v>
-      </c>
-      <c r="H14">
-        <v>0.17400769570391</v>
-      </c>
-      <c r="I14">
-        <v>8.3778986855825403E-3</v>
-      </c>
-      <c r="J14">
-        <v>0.14522613412805399</v>
-      </c>
-      <c r="K14">
-        <v>5.859375E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>36</v>
-      </c>
-      <c r="B15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15">
-        <v>10</v>
-      </c>
-      <c r="E15">
-        <v>9</v>
-      </c>
-      <c r="F15">
-        <v>0.12890625</v>
-      </c>
-      <c r="G15">
-        <v>6.04044647707732E-2</v>
-      </c>
-      <c r="H15">
-        <v>6.3700150529281699E-2</v>
-      </c>
-      <c r="I15">
-        <v>8.3778986855825403E-3</v>
-      </c>
-      <c r="J15">
-        <v>3.7182553894783102E-2</v>
-      </c>
-      <c r="K15">
-        <v>0.21484375</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>36</v>
-      </c>
-      <c r="B16" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16">
-        <v>10</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>1.953125E-3</v>
-      </c>
-      <c r="G16">
-        <v>0.17400769570391</v>
-      </c>
-      <c r="H16">
-        <v>6.3700150529281699E-2</v>
-      </c>
-      <c r="I16">
-        <v>0.14522613412805399</v>
-      </c>
-      <c r="J16">
-        <v>3.7182553894783102E-2</v>
-      </c>
-      <c r="K16">
-        <v>2.9296875E-2</v>
       </c>
     </row>
   </sheetData>
@@ -2325,10 +2323,10 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C1" t="s">
         <v>29</v>
@@ -2337,24 +2335,24 @@
         <v>30</v>
       </c>
       <c r="E1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I1" t="s">
         <v>48</v>
-      </c>
-      <c r="F1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I1" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B2">
         <v>10</v>
@@ -2378,12 +2376,12 @@
         <v>2.4739583333333301E-2</v>
       </c>
       <c r="I2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B3">
         <v>10</v>
@@ -2409,7 +2407,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B4">
         <v>10</v>
@@ -2435,7 +2433,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B5">
         <v>10</v>
@@ -2461,7 +2459,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B6">
         <v>10</v>
@@ -2487,7 +2485,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B7">
         <v>10</v>
@@ -2513,7 +2511,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B8">
         <v>10</v>
@@ -2539,7 +2537,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B9">
         <v>10</v>
@@ -2565,7 +2563,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B10">
         <v>10</v>
@@ -2591,7 +2589,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B11">
         <v>10</v>
@@ -2615,12 +2613,12 @@
         <v>2.4739583333333301E-2</v>
       </c>
       <c r="I11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B12">
         <v>10</v>
@@ -2646,7 +2644,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B13">
         <v>10</v>
@@ -2672,7 +2670,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B14">
         <v>10</v>
@@ -2698,7 +2696,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B15">
         <v>10</v>
@@ -2724,7 +2722,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B16">
         <v>10</v>
@@ -2750,7 +2748,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B17">
         <v>10</v>
@@ -2776,7 +2774,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B18">
         <v>10</v>
@@ -2800,12 +2798,12 @@
         <v>2.4739583333333301E-2</v>
       </c>
       <c r="I18" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B19">
         <v>10</v>
@@ -2831,7 +2829,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B20">
         <v>10</v>
